--- a/BluetoothClassD/BluetoothClassD.xlsx
+++ b/BluetoothClassD/BluetoothClassD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tomwatson/Documents/GitHub/Kicadprojects/BluetoothClassD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA5FF57-E128-2E45-8EBE-F7BA8774B6CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D4DA52-48F6-CC42-9794-8E6AD3E123E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6160" yWindow="3300" windowWidth="28040" windowHeight="17180" xr2:uid="{EF6F5456-4A8C-714D-AA6D-060DC6B9EA03}"/>
   </bookViews>
@@ -1751,7 +1751,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>46</v>
       </c>
@@ -1770,8 +1770,6 @@
       <c r="F22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
     </row>
     <row r="23" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
